--- a/public/tally_templates/SWAT.xlsx
+++ b/public/tally_templates/SWAT.xlsx
@@ -7231,7 +7231,6 @@
       </c>
       <c r="H54" s="369">
         <f>H12</f>
-        <v>NaN</v>
       </c>
       <c r="I54" s="53" t="s">
         <v>69</v>

--- a/public/tally_templates/SWAT.xlsx
+++ b/public/tally_templates/SWAT.xlsx
@@ -1130,7 +1130,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac x16r2">
   <numFmts count="8">
     <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * -#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* (#,##0);_(* &quot;-&quot;_);_(@_)"/>
@@ -3083,7 +3083,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="581">
+  <cellXfs count="610">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -4806,6 +4806,93 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4814,11 +4901,11 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <ns3:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <ns4:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -5086,7 +5173,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y131"/>
   <sheetFormatPr defaultRowHeight="17.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
@@ -5856,7 +5943,7 @@
       <c r="G7" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="265">
+      <c r="H7" s="602">
         <v>46225</v>
       </c>
       <c r="I7" s="265"/>
@@ -5894,7 +5981,7 @@
       <c r="G8" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="14" t="s">
+      <c r="H8" s="586" t="s">
         <v>111</v>
       </c>
       <c r="I8" s="14"/>
@@ -7089,7 +7176,7 @@
       <c r="G50" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H50" s="14" t="s">
+      <c r="H50" s="586" t="s">
         <v>111</v>
       </c>
       <c r="I50" s="14"/>
@@ -7214,27 +7301,17 @@
       <c r="Y53" s="90"/>
     </row>
     <row r="54" ht="21" customHeight="1" spans="1:25" s="40" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="53" t="s">
-        <v>122</v>
-      </c>
+      <c r="A54" s="53"/>
       <c r="B54" s="367"/>
-      <c r="C54" s="367" t="s">
-        <v>123</v>
-      </c>
+      <c r="C54" s="367"/>
       <c r="D54" s="53"/>
       <c r="E54" s="53"/>
-      <c r="F54" s="368">
-        <v>1</v>
-      </c>
-      <c r="G54" s="368">
-        <v>1</v>
-      </c>
+      <c r="F54" s="368"/>
+      <c r="G54" s="368"/>
       <c r="H54" s="369">
         <f>H12</f>
       </c>
-      <c r="I54" s="53" t="s">
-        <v>69</v>
-      </c>
+      <c r="I54" s="53"/>
       <c r="J54" s="90"/>
       <c r="K54" s="40"/>
       <c r="L54" s="40"/>
@@ -7253,27 +7330,15 @@
       <c r="Y54" s="40"/>
     </row>
     <row r="55" ht="21" customHeight="1" spans="1:25" s="40" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="234" t="s">
-        <v>124</v>
-      </c>
+      <c r="A55" s="234"/>
       <c r="B55" s="370"/>
-      <c r="C55" s="370" t="s">
-        <v>123</v>
-      </c>
+      <c r="C55" s="370"/>
       <c r="D55" s="234"/>
       <c r="E55" s="234"/>
-      <c r="F55" s="371">
-        <v>14</v>
-      </c>
-      <c r="G55" s="371">
-        <v>13.9</v>
-      </c>
-      <c r="H55" s="372" t="s">
-        <v>125</v>
-      </c>
-      <c r="I55" s="234" t="s">
-        <v>126</v>
-      </c>
+      <c r="F55" s="371"/>
+      <c r="G55" s="371"/>
+      <c r="H55" s="372"/>
+      <c r="I55" s="234"/>
       <c r="J55" s="90"/>
       <c r="K55" s="40"/>
       <c r="L55" s="40"/>
@@ -8321,7 +8386,7 @@
       <c r="G92" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H92" s="14" t="s">
+      <c r="H92" s="586" t="s">
         <v>111</v>
       </c>
       <c r="I92" s="14"/>
@@ -9541,7 +9606,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
   </sheetPr>
@@ -10339,7 +10404,7 @@
       <c r="A8" s="210" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="210" t="s">
+      <c r="B8" s="171" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="210"/>
@@ -10351,7 +10416,7 @@
         <v>39</v>
       </c>
       <c r="I8" s="192"/>
-      <c r="J8" s="192" t="s">
+      <c r="J8" s="171" t="s">
         <v>61</v>
       </c>
       <c r="K8" s="192"/>
@@ -10402,7 +10467,7 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
-    <row r="10" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="214" t="s">
         <v>11</v>
       </c>
@@ -10443,7 +10508,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
-    <row r="11" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="218"/>
       <c r="B11" s="218"/>
       <c r="C11" s="268"/>
@@ -11262,7 +11327,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
   </sheetPr>
@@ -11618,7 +11683,7 @@
       <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="581" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="1"/>
@@ -11627,14 +11692,14 @@
       <c r="F4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="12"/>
+      <c r="G4" s="582"/>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
       <c r="J4" s="1"/>
       <c r="K4" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="L4" s="13"/>
+      <c r="L4" s="583"/>
       <c r="M4" s="14"/>
       <c r="N4" s="14"/>
       <c r="O4" s="14"/>
@@ -11680,21 +11745,21 @@
       <c r="A6" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="16"/>
+      <c r="B6" s="582"/>
       <c r="C6" s="1"/>
       <c r="D6" s="2"/>
       <c r="E6" s="17"/>
       <c r="F6" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="12"/>
+      <c r="G6" s="582"/>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
       <c r="J6" s="1"/>
       <c r="K6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="L6" s="18" t="s">
+      <c r="L6" s="584" t="s">
         <v>9</v>
       </c>
       <c r="M6" s="18"/>
@@ -12527,7 +12592,7 @@
       <c r="X33" s="40"/>
       <c r="Y33" s="40"/>
     </row>
-    <row r="34" ht="12.4" customHeight="1" hidden="1" spans="1:25" s="40" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" ht="13.5" customHeight="1" hidden="1" spans="1:25" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="49"/>
       <c r="B34" s="99"/>
       <c r="C34" s="70" t="s">
@@ -12556,7 +12621,7 @@
       <c r="X34" s="40"/>
       <c r="Y34" s="40"/>
     </row>
-    <row r="35" ht="12.4" customHeight="1" hidden="1" spans="1:25" s="40" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" ht="13.5" customHeight="1" hidden="1" spans="1:25" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="49"/>
       <c r="B35" s="50"/>
       <c r="C35" s="87" t="s">
@@ -12585,7 +12650,7 @@
       <c r="X35" s="40"/>
       <c r="Y35" s="40"/>
     </row>
-    <row r="36" ht="12.4" customHeight="1" hidden="1" spans="1:25" s="40" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" ht="13.5" customHeight="1" hidden="1" spans="1:25" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="49"/>
       <c r="B36" s="50"/>
       <c r="C36" s="63" t="s">
@@ -12614,7 +12679,7 @@
       <c r="X36" s="40"/>
       <c r="Y36" s="40"/>
     </row>
-    <row r="37" ht="12.4" customHeight="1" hidden="1" spans="1:25" s="40" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" ht="13.5" customHeight="1" hidden="1" spans="1:25" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="49"/>
       <c r="B37" s="50"/>
       <c r="C37" s="87" t="s">
@@ -14348,7 +14413,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
@@ -15027,7 +15092,7 @@
       <c r="O6" s="264" t="s">
         <v>4</v>
       </c>
-      <c r="P6" s="40"/>
+      <c r="P6" s="608"/>
       <c r="Q6" s="40"/>
       <c r="R6" s="90" t="str">
         <f>'Final Work'!G4</f>
@@ -15101,7 +15166,7 @@
       </c>
       <c r="B8" s="416"/>
       <c r="C8" s="416"/>
-      <c r="D8" s="417" t="s">
+      <c r="D8" s="609" t="s">
         <v>61</v>
       </c>
       <c r="E8" s="417"/>
@@ -15117,7 +15182,7 @@
       <c r="O8" s="417" t="s">
         <v>7</v>
       </c>
-      <c r="P8" s="155"/>
+      <c r="P8" s="609"/>
       <c r="Q8" s="155"/>
       <c r="R8" s="416">
         <f>'Final Work'!G6</f>
@@ -15134,7 +15199,7 @@
       </c>
       <c r="Z8" s="416"/>
       <c r="AA8" s="416"/>
-      <c r="AB8" s="416" t="s">
+      <c r="AB8" s="609" t="s">
         <v>25</v>
       </c>
       <c r="AC8" s="416"/>
@@ -20272,7 +20337,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="60"/>
   </sheetPr>
@@ -21076,13 +21141,13 @@
       <c r="G6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="192"/>
+      <c r="H6" s="171"/>
       <c r="I6" s="192"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L6" s="13"/>
+      <c r="L6" s="583"/>
       <c r="M6" s="14"/>
       <c r="N6" s="9"/>
       <c r="O6" s="9"/>
@@ -21128,7 +21193,7 @@
       <c r="A8" s="210" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="594" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="3"/>
@@ -21138,13 +21203,13 @@
       <c r="G8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H8" s="192"/>
+      <c r="H8" s="171"/>
       <c r="I8" s="192"/>
       <c r="J8" s="3"/>
       <c r="K8" s="210" t="s">
         <v>40</v>
       </c>
-      <c r="L8" s="192"/>
+      <c r="L8" s="171"/>
       <c r="M8" s="192"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
@@ -21186,7 +21251,7 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
-    <row r="10" ht="14.45" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="211" t="s">
         <v>41</v>
       </c>
@@ -21231,7 +21296,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
-    <row r="11" ht="14.45" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="215"/>
       <c r="B11" s="216"/>
       <c r="C11" s="217"/>
@@ -21264,16 +21329,16 @@
       <c r="A12" s="219"/>
       <c r="B12" s="220"/>
       <c r="C12" s="221"/>
-      <c r="D12" s="222"/>
-      <c r="E12" s="223"/>
-      <c r="F12" s="224"/>
+      <c r="D12" s="220"/>
+      <c r="E12" s="271"/>
+      <c r="F12" s="221"/>
       <c r="G12" s="219"/>
       <c r="H12" s="225"/>
       <c r="I12" s="226"/>
       <c r="J12" s="227"/>
       <c r="K12" s="219"/>
       <c r="L12" s="219"/>
-      <c r="M12" s="228"/>
+      <c r="M12" s="595"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -21288,19 +21353,19 @@
       <c r="Y12" s="3"/>
     </row>
     <row r="13" ht="19.15" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A13" s="229"/>
+      <c r="A13" s="596"/>
       <c r="B13" s="230"/>
       <c r="C13" s="92"/>
-      <c r="D13" s="231"/>
-      <c r="E13" s="232"/>
-      <c r="F13" s="233"/>
+      <c r="D13" s="240"/>
+      <c r="E13" s="597"/>
+      <c r="F13" s="598"/>
       <c r="G13" s="234"/>
       <c r="H13" s="235"/>
       <c r="I13" s="236"/>
       <c r="J13" s="237"/>
       <c r="K13" s="234"/>
       <c r="L13" s="234"/>
-      <c r="M13" s="238"/>
+      <c r="M13" s="599"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
@@ -21315,19 +21380,19 @@
       <c r="Y13" s="3"/>
     </row>
     <row r="14" ht="19.15" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A14" s="239"/>
+      <c r="A14" s="600"/>
       <c r="B14" s="240"/>
       <c r="C14" s="204"/>
-      <c r="D14" s="231"/>
-      <c r="E14" s="232"/>
-      <c r="F14" s="233"/>
+      <c r="D14" s="240"/>
+      <c r="E14" s="597"/>
+      <c r="F14" s="598"/>
       <c r="G14" s="234"/>
       <c r="H14" s="235"/>
       <c r="I14" s="236"/>
       <c r="J14" s="237"/>
       <c r="K14" s="234"/>
       <c r="L14" s="234"/>
-      <c r="M14" s="241"/>
+      <c r="M14" s="601"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
@@ -21342,19 +21407,19 @@
       <c r="Y14" s="3"/>
     </row>
     <row r="15" ht="19.15" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A15" s="239"/>
+      <c r="A15" s="600"/>
       <c r="B15" s="240"/>
       <c r="C15" s="204"/>
-      <c r="D15" s="231"/>
-      <c r="E15" s="232"/>
-      <c r="F15" s="233"/>
+      <c r="D15" s="240"/>
+      <c r="E15" s="597"/>
+      <c r="F15" s="598"/>
       <c r="G15" s="234"/>
       <c r="H15" s="235"/>
       <c r="I15" s="236"/>
       <c r="J15" s="237"/>
       <c r="K15" s="234"/>
       <c r="L15" s="234"/>
-      <c r="M15" s="241"/>
+      <c r="M15" s="601"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
@@ -21369,19 +21434,19 @@
       <c r="Y15" s="3"/>
     </row>
     <row r="16" ht="19.15" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A16" s="239"/>
+      <c r="A16" s="600"/>
       <c r="B16" s="240"/>
       <c r="C16" s="204"/>
-      <c r="D16" s="231"/>
-      <c r="E16" s="232"/>
-      <c r="F16" s="233"/>
+      <c r="D16" s="240"/>
+      <c r="E16" s="597"/>
+      <c r="F16" s="598"/>
       <c r="G16" s="234"/>
       <c r="H16" s="235"/>
       <c r="I16" s="236"/>
       <c r="J16" s="237"/>
       <c r="K16" s="234"/>
       <c r="L16" s="234"/>
-      <c r="M16" s="241"/>
+      <c r="M16" s="601"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
@@ -21396,19 +21461,19 @@
       <c r="Y16" s="3"/>
     </row>
     <row r="17" ht="19.15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A17" s="239"/>
+      <c r="A17" s="600"/>
       <c r="B17" s="240"/>
       <c r="C17" s="204"/>
-      <c r="D17" s="231"/>
-      <c r="E17" s="232"/>
-      <c r="F17" s="233"/>
+      <c r="D17" s="240"/>
+      <c r="E17" s="597"/>
+      <c r="F17" s="598"/>
       <c r="G17" s="234"/>
       <c r="H17" s="235"/>
       <c r="I17" s="236"/>
       <c r="J17" s="237"/>
       <c r="K17" s="234"/>
       <c r="L17" s="234"/>
-      <c r="M17" s="241"/>
+      <c r="M17" s="601"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
@@ -21423,19 +21488,19 @@
       <c r="Y17" s="3"/>
     </row>
     <row r="18" ht="19.15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A18" s="239"/>
+      <c r="A18" s="600"/>
       <c r="B18" s="240"/>
       <c r="C18" s="204"/>
-      <c r="D18" s="231"/>
-      <c r="E18" s="232"/>
-      <c r="F18" s="233"/>
+      <c r="D18" s="240"/>
+      <c r="E18" s="597"/>
+      <c r="F18" s="598"/>
       <c r="G18" s="234"/>
       <c r="H18" s="235"/>
       <c r="I18" s="236"/>
       <c r="J18" s="237"/>
       <c r="K18" s="234"/>
       <c r="L18" s="234"/>
-      <c r="M18" s="241"/>
+      <c r="M18" s="601"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
@@ -21450,19 +21515,19 @@
       <c r="Y18" s="3"/>
     </row>
     <row r="19" ht="19.15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A19" s="239"/>
+      <c r="A19" s="600"/>
       <c r="B19" s="240"/>
       <c r="C19" s="204"/>
-      <c r="D19" s="231"/>
-      <c r="E19" s="232"/>
-      <c r="F19" s="233"/>
+      <c r="D19" s="240"/>
+      <c r="E19" s="597"/>
+      <c r="F19" s="598"/>
       <c r="G19" s="234"/>
       <c r="H19" s="235"/>
       <c r="I19" s="236"/>
       <c r="J19" s="237"/>
       <c r="K19" s="234"/>
       <c r="L19" s="234"/>
-      <c r="M19" s="241"/>
+      <c r="M19" s="601"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
@@ -21477,19 +21542,19 @@
       <c r="Y19" s="3"/>
     </row>
     <row r="20" ht="19.15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A20" s="239"/>
+      <c r="A20" s="600"/>
       <c r="B20" s="234"/>
       <c r="C20" s="234"/>
-      <c r="D20" s="231"/>
-      <c r="E20" s="232"/>
-      <c r="F20" s="233"/>
+      <c r="D20" s="240"/>
+      <c r="E20" s="597"/>
+      <c r="F20" s="598"/>
       <c r="G20" s="234"/>
       <c r="H20" s="235"/>
       <c r="I20" s="236"/>
       <c r="J20" s="237"/>
       <c r="K20" s="234"/>
       <c r="L20" s="234"/>
-      <c r="M20" s="241"/>
+      <c r="M20" s="601"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
@@ -21504,19 +21569,19 @@
       <c r="Y20" s="3"/>
     </row>
     <row r="21" ht="19.15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A21" s="239"/>
+      <c r="A21" s="600"/>
       <c r="B21" s="234"/>
       <c r="C21" s="234"/>
-      <c r="D21" s="231"/>
-      <c r="E21" s="232"/>
-      <c r="F21" s="233"/>
+      <c r="D21" s="240"/>
+      <c r="E21" s="597"/>
+      <c r="F21" s="598"/>
       <c r="G21" s="234"/>
       <c r="H21" s="242"/>
       <c r="I21" s="243"/>
       <c r="J21" s="237"/>
       <c r="K21" s="234"/>
       <c r="L21" s="234"/>
-      <c r="M21" s="241"/>
+      <c r="M21" s="601"/>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
@@ -21531,19 +21596,19 @@
       <c r="Y21" s="3"/>
     </row>
     <row r="22" ht="19.15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A22" s="229"/>
+      <c r="A22" s="596"/>
       <c r="B22" s="230"/>
       <c r="C22" s="92"/>
-      <c r="D22" s="231"/>
-      <c r="E22" s="232"/>
-      <c r="F22" s="233"/>
+      <c r="D22" s="240"/>
+      <c r="E22" s="597"/>
+      <c r="F22" s="598"/>
       <c r="G22" s="234"/>
       <c r="H22" s="242"/>
       <c r="I22" s="243"/>
       <c r="J22" s="237"/>
       <c r="K22" s="234"/>
       <c r="L22" s="234"/>
-      <c r="M22" s="238"/>
+      <c r="M22" s="599"/>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
@@ -22208,7 +22273,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="60"/>
   </sheetPr>
@@ -23006,7 +23071,7 @@
       <c r="A8" s="210" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="210" t="s">
+      <c r="B8" s="171" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="210"/>
@@ -23018,7 +23083,7 @@
         <v>60</v>
       </c>
       <c r="I8" s="192"/>
-      <c r="J8" s="192" t="s">
+      <c r="J8" s="171" t="s">
         <v>61</v>
       </c>
       <c r="K8" s="192"/>
@@ -23069,7 +23134,7 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
-    <row r="10" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="211" t="s">
         <v>11</v>
       </c>
@@ -23110,7 +23175,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
-    <row r="11" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="215"/>
       <c r="B11" s="215"/>
       <c r="C11" s="268"/>
@@ -23140,32 +23205,18 @@
       <c r="Y11" s="3"/>
     </row>
     <row r="12" ht="19.15" customHeight="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="B12" s="53" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" s="220" t="s">
-        <v>70</v>
-      </c>
+      <c r="A12" s="53"/>
+      <c r="B12" s="53"/>
+      <c r="C12" s="220"/>
       <c r="D12" s="271"/>
       <c r="E12" s="221"/>
-      <c r="F12" s="220" t="s">
-        <v>71</v>
-      </c>
+      <c r="F12" s="220"/>
       <c r="G12" s="271"/>
       <c r="H12" s="271"/>
       <c r="I12" s="221"/>
-      <c r="J12" s="53">
-        <v>1</v>
-      </c>
-      <c r="K12" s="53" t="s">
-        <v>52</v>
-      </c>
-      <c r="L12" s="272" t="s">
-        <v>72</v>
-      </c>
+      <c r="J12" s="53"/>
+      <c r="K12" s="53"/>
+      <c r="L12" s="272"/>
       <c r="M12" s="273"/>
       <c r="N12" s="273"/>
       <c r="O12" s="273"/>
@@ -23181,32 +23232,18 @@
       <c r="Y12" s="3"/>
     </row>
     <row r="13" ht="19.15" customHeight="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="275" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13" s="275" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="172" t="s">
-        <v>74</v>
-      </c>
+      <c r="A13" s="275"/>
+      <c r="B13" s="275"/>
+      <c r="C13" s="172"/>
       <c r="D13" s="276"/>
       <c r="E13" s="204"/>
-      <c r="F13" s="172" t="s">
-        <v>75</v>
-      </c>
+      <c r="F13" s="172"/>
       <c r="G13" s="276"/>
       <c r="H13" s="276"/>
       <c r="I13" s="204"/>
-      <c r="J13" s="275">
-        <v>1</v>
-      </c>
-      <c r="K13" s="275" t="s">
-        <v>52</v>
-      </c>
-      <c r="L13" s="185" t="s">
-        <v>76</v>
-      </c>
+      <c r="J13" s="275"/>
+      <c r="K13" s="275"/>
+      <c r="L13" s="185"/>
       <c r="M13" s="186"/>
       <c r="N13" s="186"/>
       <c r="O13" s="186"/>
@@ -23955,7 +23992,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y51"/>
   <sheetFormatPr defaultRowHeight="17.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
@@ -24619,11 +24656,11 @@
       <c r="A6" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="159"/>
+      <c r="B6" s="585"/>
       <c r="C6" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="14"/>
+      <c r="D6" s="586"/>
       <c r="E6" s="14"/>
       <c r="F6" s="9"/>
       <c r="G6" s="161" t="s">
@@ -24682,17 +24719,17 @@
       <c r="A8" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="163"/>
+      <c r="B8" s="586"/>
       <c r="C8" s="160" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="14"/>
+      <c r="D8" s="586"/>
       <c r="E8" s="14"/>
       <c r="F8" s="160"/>
       <c r="G8" s="164" t="s">
         <v>30</v>
       </c>
-      <c r="H8" s="18"/>
+      <c r="H8" s="584"/>
       <c r="I8" s="9"/>
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
@@ -24828,7 +24865,7 @@
     <row r="13" ht="18" customHeight="1" spans="1:25" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="168"/>
       <c r="B13" s="169"/>
-      <c r="C13" s="170"/>
+      <c r="C13" s="587"/>
       <c r="D13" s="170"/>
       <c r="E13" s="170"/>
       <c r="F13" s="170"/>
@@ -24855,7 +24892,7 @@
     <row r="14" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="172"/>
       <c r="B14" s="173"/>
-      <c r="C14" s="174"/>
+      <c r="C14" s="588"/>
       <c r="D14" s="175"/>
       <c r="E14" s="175"/>
       <c r="F14" s="175"/>
@@ -24882,7 +24919,7 @@
     <row r="15" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="172"/>
       <c r="B15" s="173"/>
-      <c r="C15" s="174"/>
+      <c r="C15" s="588"/>
       <c r="D15" s="175"/>
       <c r="E15" s="175"/>
       <c r="F15" s="175"/>
@@ -24909,7 +24946,7 @@
     <row r="16" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="172"/>
       <c r="B16" s="173"/>
-      <c r="C16" s="177"/>
+      <c r="C16" s="589"/>
       <c r="D16" s="177"/>
       <c r="E16" s="177"/>
       <c r="F16" s="177"/>
@@ -24936,7 +24973,7 @@
     <row r="17" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" s="178"/>
       <c r="B17" s="179"/>
-      <c r="C17" s="180"/>
+      <c r="C17" s="590"/>
       <c r="D17" s="181"/>
       <c r="E17" s="181"/>
       <c r="F17" s="181"/>
@@ -24963,7 +25000,7 @@
     <row r="18" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="183"/>
       <c r="B18" s="184"/>
-      <c r="C18" s="185"/>
+      <c r="C18" s="591"/>
       <c r="D18" s="186"/>
       <c r="E18" s="186"/>
       <c r="F18" s="186"/>
@@ -24990,7 +25027,7 @@
     <row r="19" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="188"/>
       <c r="B19" s="184"/>
-      <c r="C19" s="185"/>
+      <c r="C19" s="591"/>
       <c r="D19" s="186"/>
       <c r="E19" s="186"/>
       <c r="F19" s="186"/>
@@ -25017,7 +25054,7 @@
     <row r="20" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="172"/>
       <c r="B20" s="173"/>
-      <c r="C20" s="177"/>
+      <c r="C20" s="589"/>
       <c r="D20" s="177"/>
       <c r="E20" s="177"/>
       <c r="F20" s="177"/>
@@ -25044,7 +25081,7 @@
     <row r="21" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="189"/>
       <c r="B21" s="173"/>
-      <c r="C21" s="174"/>
+      <c r="C21" s="588"/>
       <c r="D21" s="175"/>
       <c r="E21" s="175"/>
       <c r="F21" s="175"/>
@@ -25071,7 +25108,7 @@
     <row r="22" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" s="190"/>
       <c r="B22" s="179"/>
-      <c r="C22" s="191"/>
+      <c r="C22" s="592"/>
       <c r="D22" s="191"/>
       <c r="E22" s="191"/>
       <c r="F22" s="191"/>
@@ -25098,7 +25135,7 @@
     <row r="23" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" s="183"/>
       <c r="B23" s="184"/>
-      <c r="C23" s="185"/>
+      <c r="C23" s="591"/>
       <c r="D23" s="186"/>
       <c r="E23" s="186"/>
       <c r="F23" s="186"/>
@@ -25125,7 +25162,7 @@
     <row r="24" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" s="188"/>
       <c r="B24" s="173"/>
-      <c r="C24" s="174"/>
+      <c r="C24" s="588"/>
       <c r="D24" s="175"/>
       <c r="E24" s="175"/>
       <c r="F24" s="175"/>
@@ -25152,7 +25189,7 @@
     <row r="25" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" s="172"/>
       <c r="B25" s="184"/>
-      <c r="C25" s="185"/>
+      <c r="C25" s="591"/>
       <c r="D25" s="186"/>
       <c r="E25" s="186"/>
       <c r="F25" s="186"/>
@@ -25179,7 +25216,7 @@
     <row r="26" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" s="193"/>
       <c r="B26" s="184"/>
-      <c r="C26" s="185"/>
+      <c r="C26" s="591"/>
       <c r="D26" s="186"/>
       <c r="E26" s="186"/>
       <c r="F26" s="186"/>
@@ -25206,7 +25243,7 @@
     <row r="27" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" s="190"/>
       <c r="B27" s="179"/>
-      <c r="C27" s="180"/>
+      <c r="C27" s="590"/>
       <c r="D27" s="181"/>
       <c r="E27" s="181"/>
       <c r="F27" s="181"/>
@@ -25233,7 +25270,7 @@
     <row r="28" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" s="194"/>
       <c r="B28" s="27"/>
-      <c r="C28" s="195"/>
+      <c r="C28" s="593"/>
       <c r="D28" s="196"/>
       <c r="E28" s="196"/>
       <c r="F28" s="196"/>
@@ -25260,7 +25297,7 @@
     <row r="29" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="193"/>
       <c r="B29" s="184"/>
-      <c r="C29" s="185"/>
+      <c r="C29" s="591"/>
       <c r="D29" s="186"/>
       <c r="E29" s="186"/>
       <c r="F29" s="186"/>
@@ -25287,7 +25324,7 @@
     <row r="30" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" s="198"/>
       <c r="B30" s="173"/>
-      <c r="C30" s="177"/>
+      <c r="C30" s="589"/>
       <c r="D30" s="177"/>
       <c r="E30" s="177"/>
       <c r="F30" s="177"/>
@@ -25314,7 +25351,7 @@
     <row r="31" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="172"/>
       <c r="B31" s="184"/>
-      <c r="C31" s="185"/>
+      <c r="C31" s="591"/>
       <c r="D31" s="186"/>
       <c r="E31" s="186"/>
       <c r="F31" s="186"/>
@@ -25341,7 +25378,7 @@
     <row r="32" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" s="178"/>
       <c r="B32" s="179"/>
-      <c r="C32" s="180"/>
+      <c r="C32" s="590"/>
       <c r="D32" s="181"/>
       <c r="E32" s="181"/>
       <c r="F32" s="181"/>
@@ -25368,7 +25405,7 @@
     <row r="33" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="29"/>
       <c r="B33" s="184"/>
-      <c r="C33" s="185"/>
+      <c r="C33" s="591"/>
       <c r="D33" s="186"/>
       <c r="E33" s="186"/>
       <c r="F33" s="186"/>
@@ -25395,7 +25432,7 @@
     <row r="34" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" s="172"/>
       <c r="B34" s="184"/>
-      <c r="C34" s="185"/>
+      <c r="C34" s="591"/>
       <c r="D34" s="186"/>
       <c r="E34" s="186"/>
       <c r="F34" s="186"/>
@@ -25422,7 +25459,7 @@
     <row r="35" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" s="199"/>
       <c r="B35" s="173"/>
-      <c r="C35" s="185"/>
+      <c r="C35" s="591"/>
       <c r="D35" s="186"/>
       <c r="E35" s="186"/>
       <c r="F35" s="186"/>
@@ -25449,7 +25486,7 @@
     <row r="36" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" s="200"/>
       <c r="B36" s="184"/>
-      <c r="C36" s="174"/>
+      <c r="C36" s="588"/>
       <c r="D36" s="175"/>
       <c r="E36" s="175"/>
       <c r="F36" s="175"/>
@@ -25476,7 +25513,7 @@
     <row r="37" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" s="201"/>
       <c r="B37" s="179"/>
-      <c r="C37" s="180"/>
+      <c r="C37" s="590"/>
       <c r="D37" s="181"/>
       <c r="E37" s="181"/>
       <c r="F37" s="181"/>
@@ -25503,7 +25540,7 @@
     <row r="38" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" s="202"/>
       <c r="B38" s="203"/>
-      <c r="C38" s="195"/>
+      <c r="C38" s="593"/>
       <c r="D38" s="196"/>
       <c r="E38" s="196"/>
       <c r="F38" s="196"/>
@@ -25530,7 +25567,7 @@
     <row r="39" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" s="200"/>
       <c r="B39" s="56"/>
-      <c r="C39" s="177"/>
+      <c r="C39" s="589"/>
       <c r="D39" s="177"/>
       <c r="E39" s="177"/>
       <c r="F39" s="177"/>
@@ -25557,7 +25594,7 @@
     <row r="40" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40" s="200"/>
       <c r="B40" s="173"/>
-      <c r="C40" s="177"/>
+      <c r="C40" s="589"/>
       <c r="D40" s="177"/>
       <c r="E40" s="177"/>
       <c r="F40" s="177"/>
@@ -25584,7 +25621,7 @@
     <row r="41" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41" s="172"/>
       <c r="B41" s="204"/>
-      <c r="C41" s="174"/>
+      <c r="C41" s="588"/>
       <c r="D41" s="175"/>
       <c r="E41" s="175"/>
       <c r="F41" s="175"/>
@@ -25611,7 +25648,7 @@
     <row r="42" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42" s="172"/>
       <c r="B42" s="56"/>
-      <c r="C42" s="185"/>
+      <c r="C42" s="591"/>
       <c r="D42" s="186"/>
       <c r="E42" s="186"/>
       <c r="F42" s="186"/>
@@ -25881,7 +25918,7 @@
       <c r="Y51" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="41">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="C3:F3"/>
@@ -25921,6 +25958,8 @@
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="A46:B46"/>
     <mergeCell ref="G46:H46"/>
+    <mergeCell ref="C43:H43"/>
+    <mergeCell ref="C44:H44"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.4724409448818898" right="0.4724409448818898" top="0.5905511811023623" bottom="0" header="0.5118110236220472" footer="0.35433070866141736"/>
@@ -25929,7 +25968,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
   </sheetPr>
@@ -26733,13 +26772,13 @@
       <c r="G6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="192"/>
+      <c r="H6" s="171"/>
       <c r="I6" s="192"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L6" s="265"/>
+      <c r="L6" s="602"/>
       <c r="M6" s="265"/>
       <c r="N6" s="1"/>
       <c r="O6" s="3"/>
@@ -26785,7 +26824,7 @@
       <c r="A8" s="210" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="594" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="278"/>
@@ -26795,13 +26834,13 @@
       <c r="G8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H8" s="192"/>
+      <c r="H8" s="171"/>
       <c r="I8" s="192"/>
       <c r="J8" s="3"/>
       <c r="K8" s="210" t="s">
         <v>40</v>
       </c>
-      <c r="L8" s="192"/>
+      <c r="L8" s="171"/>
       <c r="M8" s="192"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
@@ -26843,7 +26882,7 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
-    <row r="10" ht="14.45" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="279" t="s">
         <v>41</v>
       </c>
@@ -26888,7 +26927,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
-    <row r="11" ht="14.45" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="215"/>
       <c r="B11" s="216"/>
       <c r="C11" s="217"/>
@@ -26921,16 +26960,16 @@
       <c r="A12" s="53"/>
       <c r="B12" s="240"/>
       <c r="C12" s="204"/>
-      <c r="D12" s="231"/>
-      <c r="E12" s="232"/>
-      <c r="F12" s="233"/>
+      <c r="D12" s="240"/>
+      <c r="E12" s="597"/>
+      <c r="F12" s="598"/>
       <c r="G12" s="234"/>
       <c r="H12" s="235"/>
       <c r="I12" s="236"/>
       <c r="J12" s="237"/>
       <c r="K12" s="234"/>
       <c r="L12" s="234"/>
-      <c r="M12" s="280"/>
+      <c r="M12" s="85"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -26948,16 +26987,16 @@
       <c r="A13" s="53"/>
       <c r="B13" s="240"/>
       <c r="C13" s="204"/>
-      <c r="D13" s="231"/>
-      <c r="E13" s="232"/>
-      <c r="F13" s="233"/>
+      <c r="D13" s="240"/>
+      <c r="E13" s="597"/>
+      <c r="F13" s="598"/>
       <c r="G13" s="234"/>
       <c r="H13" s="235"/>
       <c r="I13" s="236"/>
       <c r="J13" s="237"/>
       <c r="K13" s="234"/>
       <c r="L13" s="234"/>
-      <c r="M13" s="280"/>
+      <c r="M13" s="85"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
@@ -26975,16 +27014,16 @@
       <c r="A14" s="53"/>
       <c r="B14" s="240"/>
       <c r="C14" s="204"/>
-      <c r="D14" s="231"/>
-      <c r="E14" s="232"/>
-      <c r="F14" s="233"/>
+      <c r="D14" s="240"/>
+      <c r="E14" s="597"/>
+      <c r="F14" s="598"/>
       <c r="G14" s="234"/>
       <c r="H14" s="235"/>
       <c r="I14" s="236"/>
       <c r="J14" s="237"/>
       <c r="K14" s="234"/>
       <c r="L14" s="234"/>
-      <c r="M14" s="280"/>
+      <c r="M14" s="85"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
@@ -27002,16 +27041,16 @@
       <c r="A15" s="53"/>
       <c r="B15" s="240"/>
       <c r="C15" s="204"/>
-      <c r="D15" s="231"/>
-      <c r="E15" s="232"/>
-      <c r="F15" s="233"/>
+      <c r="D15" s="240"/>
+      <c r="E15" s="597"/>
+      <c r="F15" s="598"/>
       <c r="G15" s="234"/>
       <c r="H15" s="235"/>
       <c r="I15" s="236"/>
       <c r="J15" s="237"/>
       <c r="K15" s="234"/>
       <c r="L15" s="234"/>
-      <c r="M15" s="280"/>
+      <c r="M15" s="85"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
@@ -27029,16 +27068,16 @@
       <c r="A16" s="53"/>
       <c r="B16" s="53"/>
       <c r="C16" s="53"/>
-      <c r="D16" s="281"/>
-      <c r="E16" s="282"/>
-      <c r="F16" s="283"/>
+      <c r="D16" s="193"/>
+      <c r="E16" s="603"/>
+      <c r="F16" s="604"/>
       <c r="G16" s="53"/>
       <c r="H16" s="235"/>
       <c r="I16" s="236"/>
       <c r="J16" s="237"/>
       <c r="K16" s="234"/>
       <c r="L16" s="234"/>
-      <c r="M16" s="280"/>
+      <c r="M16" s="85"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
@@ -27056,16 +27095,16 @@
       <c r="A17" s="53"/>
       <c r="B17" s="240"/>
       <c r="C17" s="204"/>
-      <c r="D17" s="231"/>
-      <c r="E17" s="232"/>
-      <c r="F17" s="233"/>
+      <c r="D17" s="240"/>
+      <c r="E17" s="597"/>
+      <c r="F17" s="598"/>
       <c r="G17" s="234"/>
       <c r="H17" s="235"/>
       <c r="I17" s="236"/>
       <c r="J17" s="237"/>
       <c r="K17" s="234"/>
       <c r="L17" s="234"/>
-      <c r="M17" s="280"/>
+      <c r="M17" s="85"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
@@ -27083,16 +27122,16 @@
       <c r="A18" s="53"/>
       <c r="B18" s="240"/>
       <c r="C18" s="204"/>
-      <c r="D18" s="231"/>
-      <c r="E18" s="232"/>
-      <c r="F18" s="233"/>
+      <c r="D18" s="240"/>
+      <c r="E18" s="597"/>
+      <c r="F18" s="598"/>
       <c r="G18" s="234"/>
       <c r="H18" s="235"/>
       <c r="I18" s="236"/>
       <c r="J18" s="237"/>
       <c r="K18" s="53"/>
       <c r="L18" s="53"/>
-      <c r="M18" s="280"/>
+      <c r="M18" s="85"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
@@ -27110,16 +27149,16 @@
       <c r="A19" s="53"/>
       <c r="B19" s="240"/>
       <c r="C19" s="204"/>
-      <c r="D19" s="231"/>
-      <c r="E19" s="232"/>
-      <c r="F19" s="233"/>
+      <c r="D19" s="240"/>
+      <c r="E19" s="597"/>
+      <c r="F19" s="598"/>
       <c r="G19" s="234"/>
       <c r="H19" s="235"/>
       <c r="I19" s="236"/>
       <c r="J19" s="237"/>
       <c r="K19" s="234"/>
       <c r="L19" s="234"/>
-      <c r="M19" s="280"/>
+      <c r="M19" s="85"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
@@ -27137,16 +27176,16 @@
       <c r="A20" s="53"/>
       <c r="B20" s="240"/>
       <c r="C20" s="204"/>
-      <c r="D20" s="231"/>
-      <c r="E20" s="232"/>
-      <c r="F20" s="233"/>
+      <c r="D20" s="240"/>
+      <c r="E20" s="597"/>
+      <c r="F20" s="598"/>
       <c r="G20" s="234"/>
       <c r="H20" s="235"/>
       <c r="I20" s="236"/>
       <c r="J20" s="237"/>
       <c r="K20" s="234"/>
       <c r="L20" s="234"/>
-      <c r="M20" s="280"/>
+      <c r="M20" s="85"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
@@ -27164,16 +27203,16 @@
       <c r="A21" s="53"/>
       <c r="B21" s="240"/>
       <c r="C21" s="204"/>
-      <c r="D21" s="231"/>
-      <c r="E21" s="232"/>
-      <c r="F21" s="233"/>
+      <c r="D21" s="240"/>
+      <c r="E21" s="597"/>
+      <c r="F21" s="598"/>
       <c r="G21" s="234"/>
       <c r="H21" s="235"/>
       <c r="I21" s="236"/>
       <c r="J21" s="237"/>
       <c r="K21" s="234"/>
       <c r="L21" s="234"/>
-      <c r="M21" s="280"/>
+      <c r="M21" s="85"/>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
@@ -27191,16 +27230,16 @@
       <c r="A22" s="53"/>
       <c r="B22" s="240"/>
       <c r="C22" s="204"/>
-      <c r="D22" s="231"/>
-      <c r="E22" s="232"/>
-      <c r="F22" s="233"/>
+      <c r="D22" s="240"/>
+      <c r="E22" s="597"/>
+      <c r="F22" s="598"/>
       <c r="G22" s="234"/>
       <c r="H22" s="235"/>
       <c r="I22" s="236"/>
       <c r="J22" s="237"/>
       <c r="K22" s="234"/>
       <c r="L22" s="234"/>
-      <c r="M22" s="280"/>
+      <c r="M22" s="85"/>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
@@ -27218,16 +27257,16 @@
       <c r="A23" s="53"/>
       <c r="B23" s="240"/>
       <c r="C23" s="204"/>
-      <c r="D23" s="231"/>
-      <c r="E23" s="232"/>
-      <c r="F23" s="233"/>
+      <c r="D23" s="240"/>
+      <c r="E23" s="597"/>
+      <c r="F23" s="598"/>
       <c r="G23" s="234"/>
       <c r="H23" s="235"/>
       <c r="I23" s="236"/>
       <c r="J23" s="237"/>
       <c r="K23" s="234"/>
       <c r="L23" s="80"/>
-      <c r="M23" s="280"/>
+      <c r="M23" s="85"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
@@ -27245,16 +27284,16 @@
       <c r="A24" s="53"/>
       <c r="B24" s="240"/>
       <c r="C24" s="204"/>
-      <c r="D24" s="231"/>
-      <c r="E24" s="232"/>
-      <c r="F24" s="233"/>
+      <c r="D24" s="240"/>
+      <c r="E24" s="597"/>
+      <c r="F24" s="598"/>
       <c r="G24" s="234"/>
       <c r="H24" s="235"/>
       <c r="I24" s="236"/>
       <c r="J24" s="237"/>
       <c r="K24" s="234"/>
       <c r="L24" s="80"/>
-      <c r="M24" s="284"/>
+      <c r="M24" s="605"/>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
@@ -28018,7 +28057,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y79"/>
   <sheetFormatPr defaultRowHeight="17.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
@@ -28698,7 +28737,7 @@
       <c r="F4" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="G4" s="265"/>
+      <c r="G4" s="602"/>
       <c r="H4" s="265"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
@@ -28761,7 +28800,7 @@
       <c r="F6" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="G6" s="303" t="s">
+      <c r="G6" s="606" t="s">
         <v>25</v>
       </c>
       <c r="H6" s="3"/>
@@ -29404,12 +29443,12 @@
     <row r="29" ht="24" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="327"/>
       <c r="B29" s="328"/>
-      <c r="C29" s="329"/>
-      <c r="D29" s="329"/>
-      <c r="E29" s="329"/>
-      <c r="F29" s="329"/>
-      <c r="G29" s="329"/>
-      <c r="H29" s="329"/>
+      <c r="C29" s="607"/>
+      <c r="D29" s="607"/>
+      <c r="E29" s="607"/>
+      <c r="F29" s="607"/>
+      <c r="G29" s="607"/>
+      <c r="H29" s="607"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
@@ -29431,12 +29470,12 @@
     <row r="30" ht="24" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" s="327"/>
       <c r="B30" s="328"/>
-      <c r="C30" s="329"/>
-      <c r="D30" s="329"/>
-      <c r="E30" s="329"/>
-      <c r="F30" s="329"/>
-      <c r="G30" s="329"/>
-      <c r="H30" s="329"/>
+      <c r="C30" s="607"/>
+      <c r="D30" s="607"/>
+      <c r="E30" s="607"/>
+      <c r="F30" s="607"/>
+      <c r="G30" s="607"/>
+      <c r="H30" s="607"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
@@ -29458,12 +29497,12 @@
     <row r="31" ht="24" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="327"/>
       <c r="B31" s="328"/>
-      <c r="C31" s="329"/>
-      <c r="D31" s="329"/>
-      <c r="E31" s="329"/>
-      <c r="F31" s="329"/>
-      <c r="G31" s="329"/>
-      <c r="H31" s="329"/>
+      <c r="C31" s="607"/>
+      <c r="D31" s="607"/>
+      <c r="E31" s="607"/>
+      <c r="F31" s="607"/>
+      <c r="G31" s="607"/>
+      <c r="H31" s="607"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
@@ -29828,7 +29867,7 @@
       <c r="F43" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="G43" s="303" t="s">
+      <c r="G43" s="606" t="s">
         <v>25</v>
       </c>
       <c r="H43" s="3"/>
@@ -30010,24 +30049,14 @@
       <c r="Y48" s="3"/>
     </row>
     <row r="49" ht="24" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A49" s="314" t="s">
-        <v>102</v>
-      </c>
+      <c r="A49" s="314"/>
       <c r="B49" s="314"/>
-      <c r="C49" s="334" t="s">
-        <v>103</v>
-      </c>
-      <c r="D49" s="314" t="s">
-        <v>13</v>
-      </c>
+      <c r="C49" s="334"/>
+      <c r="D49" s="314"/>
       <c r="E49" s="314"/>
-      <c r="F49" s="335" t="s">
-        <v>104</v>
-      </c>
+      <c r="F49" s="335"/>
       <c r="G49" s="314"/>
-      <c r="H49" s="314" t="s">
-        <v>105</v>
-      </c>
+      <c r="H49" s="314"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
       <c r="K49" s="3"/>
